--- a/task125/golden/hls_visit_limit_path_2027.xlsx
+++ b/task125/golden/hls_visit_limit_path_2027.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>HLS: gap in the published rates from the three-visit cap, six visits from January 2027</t>
-  </si>
-  <si>
-    <t>Percentage points, published rate less the rate with six first-interview visits throughout. People aged 15 and over. Assessed on April to June 2026 (methods note, section 5).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>HLS: gap in the published rates from the three-visit cap, six visits from 1 April 2027</t>
+  </si>
+  <si>
+    <t>Percentage points, published rate less the rate with six first-interview visits throughout. People aged 15 and over. Simulated on Jan-Mar 2026, the one quarter whose five intakes were all interviewed on six visits and all carry visit histories.</t>
   </si>
   <si>
     <t>Quarter</t>
@@ -53,7 +53,7 @@
     <t>Jul-Sep 2027</t>
   </si>
   <si>
-    <t>July to September 2026</t>
+    <t>April to June to July to September 2026</t>
   </si>
   <si>
     <t>Unemployment rate</t>
@@ -68,7 +68,16 @@
     <t>Published, July to September 2026</t>
   </si>
   <si>
-    <t>July to September 2026 without the cap</t>
+    <t>Gap, April to June 2026</t>
+  </si>
+  <si>
+    <t>Gap, July to September 2026</t>
+  </si>
+  <si>
+    <t>April to June 2026 on six visits throughout</t>
+  </si>
+  <si>
+    <t>July to September 2026 on six visits throughout</t>
   </si>
   <si>
     <t>Change, published</t>
@@ -128,7 +137,7 @@
     <t>Hours: hours actually worked in the reference week by employed people, weighted with the final person weights; telephone interviews record hours and minutes.</t>
   </si>
   <si>
-    <t>Gaps are rounded independently from unrounded estimates.</t>
+    <t>Gaps are rounded independently from unrounded estimates. The cap applies to the intakes of April to June 2026 to January to March 2027.</t>
   </si>
   <si>
     <t>Source: HLS extract of 20 October 2026; Merrowland Statistics, Labour Market Statistics.</t>
@@ -508,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5324925-4A48-5389-9544-F8B97EBF9DD4}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -542,10 +551,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.74</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,10 +562,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>0.37</v>
+        <v>0.53</v>
       </c>
       <c r="C6" s="4">
-        <v>-1.37</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -564,10 +573,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="C7" s="4">
-        <v>-1.11</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -575,10 +584,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="C8" s="4">
-        <v>-0.93</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -586,10 +595,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="C9" s="4">
-        <v>-0.63</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25"/>
@@ -609,10 +618,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="5">
-        <v>4.99</v>
+        <v>5.59</v>
       </c>
       <c r="C12" s="5">
-        <v>60.01</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -620,21 +629,21 @@
         <v>14</v>
       </c>
       <c r="B13" s="5">
-        <v>5.27</v>
+        <v>5.86</v>
       </c>
       <c r="C13" s="5">
-        <v>59.36</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="5">
-        <v>5.04</v>
-      </c>
-      <c r="C14" s="5">
-        <v>60.1</v>
+      <c r="B14" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="C14" s="4">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -642,32 +651,65 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="C15" s="4">
-        <v>-0.65</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="4">
-        <v>0.22</v>
-      </c>
-      <c r="C16" s="4">
-        <v>-0.74</v>
+      <c r="B16" s="5">
+        <v>5.38</v>
+      </c>
+      <c r="C16" s="5">
+        <v>59.67</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="5">
+        <v>5.47</v>
+      </c>
+      <c r="C17" s="5">
+        <v>59.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="C18" s="4">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="C19" s="4">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="4">
         <v>0.09</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -690,147 +732,147 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6">
-        <v>3945</v>
+        <v>3866</v>
       </c>
       <c r="C4">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D4">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E4" s="5">
-        <v>30.77</v>
+        <v>31.65</v>
       </c>
       <c r="F4" s="7">
-        <v>27055.5</v>
+        <v>26679.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="6">
-        <v>2360</v>
+        <v>2378</v>
       </c>
       <c r="C5">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" s="5">
-        <v>30.58</v>
+        <v>25.19</v>
       </c>
       <c r="F5" s="7">
-        <v>16009.7</v>
+        <v>16125.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="6">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="C6">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E6" s="5">
-        <v>35.45</v>
+        <v>37.96</v>
       </c>
       <c r="F6" s="7">
-        <v>12455.6</v>
+        <v>12659.2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" s="6">
-        <v>1737</v>
+        <v>1629</v>
       </c>
       <c r="C7">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5">
-        <v>39.22</v>
+        <v>24.11</v>
       </c>
       <c r="F7" s="7">
-        <v>11070.1</v>
+        <v>10623.9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" s="6">
-        <v>1469</v>
+        <v>1408</v>
       </c>
       <c r="C8">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5">
-        <v>28.72</v>
+        <v>30.12</v>
       </c>
       <c r="F8" s="7">
-        <v>9858.6</v>
+        <v>9735.5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6">
-        <v>1212</v>
+        <v>1282</v>
       </c>
       <c r="C9">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E9" s="5">
-        <v>27.14</v>
+        <v>29.03</v>
       </c>
       <c r="F9" s="7">
-        <v>8103.1</v>
+        <v>7648.6</v>
       </c>
     </row>
   </sheetData>
@@ -848,27 +890,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/task125/golden/hls_visit_limit_path_2027.xlsx
+++ b/task125/golden/hls_visit_limit_path_2027.xlsx
@@ -772,7 +772,7 @@
         <v>31.65</v>
       </c>
       <c r="F4" s="7">
-        <v>26679.2</v>
+        <v>26679.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -792,7 +792,7 @@
         <v>25.19</v>
       </c>
       <c r="F5" s="7">
-        <v>16125.5</v>
+        <v>16124.7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -812,7 +812,7 @@
         <v>37.96</v>
       </c>
       <c r="F6" s="7">
-        <v>12659.2</v>
+        <v>12659.1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,7 +832,7 @@
         <v>24.11</v>
       </c>
       <c r="F7" s="7">
-        <v>10623.9</v>
+        <v>10624.5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>30.12</v>
       </c>
       <c r="F8" s="7">
-        <v>9735.5</v>
+        <v>9734</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -872,7 +872,7 @@
         <v>29.03</v>
       </c>
       <c r="F9" s="7">
-        <v>7648.6</v>
+        <v>7648.3</v>
       </c>
     </row>
   </sheetData>
